--- a/DataTables/Datas/#ArmyData-小队表.xlsx
+++ b/DataTables/Datas/#ArmyData-小队表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="134">
   <si>
     <t>##var</t>
   </si>
@@ -99,6 +99,9 @@
   </si>
   <si>
     <t>int</t>
+  </si>
+  <si>
+    <t>float</t>
   </si>
   <si>
     <t>string#ref=TbMultiLanguageText?</t>
@@ -438,7 +441,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -451,13 +454,6 @@
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -604,7 +600,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -691,12 +687,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -710,12 +700,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -806,12 +790,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -954,97 +932,103 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1053,10 +1037,10 @@
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1065,10 +1049,10 @@
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1077,25 +1061,19 @@
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1576,19 +1554,19 @@
         <v>23</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N2" s="7" t="s">
         <v>23</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P2" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q2" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R2" s="7" t="s">
         <v>23</v>
@@ -1599,7 +1577,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -1622,70 +1600,70 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R4" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="S4" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:19">
       <c r="B5" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E5" s="8">
         <v>26</v>
@@ -1715,7 +1693,7 @@
       </c>
       <c r="O5" s="8"/>
       <c r="P5" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q5" s="8"/>
       <c r="R5" s="8"/>
@@ -1723,13 +1701,13 @@
     </row>
     <row r="6" s="1" customFormat="1" spans="1:19">
       <c r="B6" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E6" s="8">
         <v>36</v>
@@ -1759,10 +1737,10 @@
       </c>
       <c r="O6" s="8"/>
       <c r="P6" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R6" s="8">
         <v>1</v>
@@ -1771,13 +1749,13 @@
     </row>
     <row r="7" s="1" customFormat="1" spans="1:19">
       <c r="B7" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E7" s="8">
         <v>40</v>
@@ -1807,10 +1785,10 @@
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q7" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R7" s="8">
         <v>2</v>
@@ -1819,13 +1797,13 @@
     </row>
     <row r="8" s="1" customFormat="1" spans="1:19">
       <c r="B8" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E8" s="8">
         <v>16</v>
@@ -1859,7 +1837,7 @@
       </c>
       <c r="O8" s="8"/>
       <c r="P8" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
@@ -1867,13 +1845,13 @@
     </row>
     <row r="9" s="1" customFormat="1" spans="1:19">
       <c r="B9" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E9" s="8">
         <v>22</v>
@@ -1907,10 +1885,10 @@
       </c>
       <c r="O9" s="8"/>
       <c r="P9" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q9" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="R9" s="8">
         <v>1</v>
@@ -1919,13 +1897,13 @@
     </row>
     <row r="10" s="1" customFormat="1" spans="1:19">
       <c r="B10" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E10" s="8">
         <v>58</v>
@@ -1955,7 +1933,7 @@
       </c>
       <c r="O10" s="8"/>
       <c r="P10" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q10" s="8"/>
       <c r="R10" s="8"/>
@@ -1963,13 +1941,13 @@
     </row>
     <row r="11" s="1" customFormat="1" spans="1:19">
       <c r="B11" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E11" s="8">
         <v>72</v>
@@ -1999,10 +1977,10 @@
       </c>
       <c r="O11" s="8"/>
       <c r="P11" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="R11" s="8">
         <v>1</v>
@@ -2011,13 +1989,13 @@
     </row>
     <row r="12" s="1" customFormat="1" spans="1:19">
       <c r="B12" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E12" s="8">
         <v>65</v>
@@ -2047,7 +2025,7 @@
       </c>
       <c r="O12" s="8"/>
       <c r="P12" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q12" s="8"/>
       <c r="R12" s="8"/>
@@ -2055,13 +2033,13 @@
     </row>
     <row r="13" s="1" customFormat="1" spans="1:19">
       <c r="B13" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E13" s="8">
         <v>75</v>
@@ -2093,10 +2071,10 @@
       </c>
       <c r="O13" s="8"/>
       <c r="P13" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q13" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R13" s="8">
         <v>1</v>
@@ -2105,13 +2083,13 @@
     </row>
     <row r="14" s="1" customFormat="1" spans="1:19">
       <c r="B14" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E14" s="8">
         <v>1000</v>
@@ -2139,7 +2117,7 @@
       <c r="N14" s="8"/>
       <c r="O14" s="8"/>
       <c r="P14" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q14" s="8"/>
       <c r="R14" s="8"/>
@@ -2167,13 +2145,13 @@
     </row>
     <row r="16" s="2" customFormat="1" spans="1:19">
       <c r="B16" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E16" s="9">
         <v>18</v>
@@ -2203,7 +2181,7 @@
       </c>
       <c r="O16" s="9"/>
       <c r="P16" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q16" s="9"/>
       <c r="R16" s="9"/>
@@ -2211,13 +2189,13 @@
     </row>
     <row r="17" s="2" customFormat="1" spans="2:19">
       <c r="B17" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" s="9" t="s">
         <v>73</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>72</v>
       </c>
       <c r="E17" s="9">
         <v>25</v>
@@ -2247,10 +2225,10 @@
       </c>
       <c r="O17" s="9"/>
       <c r="P17" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q17" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="R17" s="9">
         <v>1</v>
@@ -2259,13 +2237,13 @@
     </row>
     <row r="18" s="2" customFormat="1" spans="2:19">
       <c r="B18" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E18" s="9">
         <v>15</v>
@@ -2299,7 +2277,7 @@
       </c>
       <c r="O18" s="9"/>
       <c r="P18" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q18" s="9"/>
       <c r="R18" s="9"/>
@@ -2307,13 +2285,13 @@
     </row>
     <row r="19" s="2" customFormat="1" spans="2:19">
       <c r="B19" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E19" s="9">
         <v>18</v>
@@ -2347,10 +2325,10 @@
       </c>
       <c r="O19" s="9"/>
       <c r="P19" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q19" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R19" s="9">
         <v>1</v>
@@ -2359,13 +2337,13 @@
     </row>
     <row r="20" s="2" customFormat="1" spans="2:19">
       <c r="B20" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E20" s="9">
         <v>40</v>
@@ -2395,7 +2373,7 @@
       </c>
       <c r="O20" s="9"/>
       <c r="P20" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q20" s="9"/>
       <c r="R20" s="9"/>
@@ -2403,13 +2381,13 @@
     </row>
     <row r="21" s="2" customFormat="1" spans="2:19">
       <c r="B21" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E21" s="9">
         <v>48</v>
@@ -2439,10 +2417,10 @@
       </c>
       <c r="O21" s="9"/>
       <c r="P21" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q21" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R21" s="9">
         <v>1</v>
@@ -2451,13 +2429,13 @@
     </row>
     <row r="22" s="2" customFormat="1" spans="2:19">
       <c r="B22" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E22" s="9">
         <v>75</v>
@@ -2487,10 +2465,10 @@
       </c>
       <c r="O22" s="9"/>
       <c r="P22" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q22" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R22" s="9">
         <v>2</v>
@@ -2499,13 +2477,13 @@
     </row>
     <row r="23" s="2" customFormat="1" spans="2:19">
       <c r="B23" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E23" s="9">
         <v>120</v>
@@ -2535,7 +2513,7 @@
       </c>
       <c r="O23" s="9"/>
       <c r="P23" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q23" s="9"/>
       <c r="R23" s="9"/>
@@ -2563,13 +2541,13 @@
     </row>
     <row r="25" s="3" customFormat="1" spans="2:19">
       <c r="B25" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E25" s="10">
         <v>22</v>
@@ -2599,7 +2577,7 @@
       </c>
       <c r="O25" s="10"/>
       <c r="P25" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -2607,13 +2585,13 @@
     </row>
     <row r="26" s="3" customFormat="1" spans="2:19">
       <c r="B26" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D26" s="10" t="s">
         <v>90</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>89</v>
       </c>
       <c r="E26" s="10">
         <v>28</v>
@@ -2643,10 +2621,10 @@
       </c>
       <c r="O26" s="10"/>
       <c r="P26" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q26" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="R26" s="10">
         <v>1</v>
@@ -2655,13 +2633,13 @@
     </row>
     <row r="27" s="3" customFormat="1" spans="2:19">
       <c r="B27" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E27" s="10">
         <v>14</v>
@@ -2695,7 +2673,7 @@
       </c>
       <c r="O27" s="10"/>
       <c r="P27" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -2703,13 +2681,13 @@
     </row>
     <row r="28" s="3" customFormat="1" spans="2:19">
       <c r="B28" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E28" s="10">
         <v>27</v>
@@ -2743,10 +2721,10 @@
       </c>
       <c r="O28" s="10"/>
       <c r="P28" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q28" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R28" s="10">
         <v>1</v>
@@ -2755,13 +2733,13 @@
     </row>
     <row r="29" s="3" customFormat="1" spans="2:19">
       <c r="B29" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E29" s="10">
         <v>200</v>
@@ -2795,10 +2773,10 @@
       </c>
       <c r="O29" s="10"/>
       <c r="P29" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q29" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R29" s="10">
         <v>2</v>
@@ -2807,13 +2785,13 @@
     </row>
     <row r="30" s="3" customFormat="1" spans="2:19">
       <c r="B30" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E30" s="10">
         <v>54</v>
@@ -2843,7 +2821,7 @@
       </c>
       <c r="O30" s="10"/>
       <c r="P30" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q30" s="10"/>
       <c r="R30" s="10"/>
@@ -2851,13 +2829,13 @@
     </row>
     <row r="31" s="3" customFormat="1" spans="2:19">
       <c r="B31" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E31" s="10">
         <v>67</v>
@@ -2887,10 +2865,10 @@
       </c>
       <c r="O31" s="10"/>
       <c r="P31" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q31" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="R31" s="10">
         <v>1</v>
@@ -2899,13 +2877,13 @@
     </row>
     <row r="32" s="3" customFormat="1" spans="2:19">
       <c r="B32" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E32" s="10">
         <v>55</v>
@@ -2939,7 +2917,7 @@
       </c>
       <c r="O32" s="10"/>
       <c r="P32" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q32" s="10"/>
       <c r="R32" s="10"/>
@@ -2947,13 +2925,13 @@
     </row>
     <row r="33" s="3" customFormat="1" spans="2:19">
       <c r="B33" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E33" s="10">
         <v>65</v>
@@ -2987,10 +2965,10 @@
       </c>
       <c r="O33" s="10"/>
       <c r="P33" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q33" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="R33" s="10">
         <v>1</v>
@@ -3019,13 +2997,13 @@
     </row>
     <row r="35" s="4" customFormat="1" spans="2:19">
       <c r="B35" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E35" s="11">
         <v>18</v>
@@ -3055,7 +3033,7 @@
       </c>
       <c r="O35" s="11"/>
       <c r="P35" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q35" s="11"/>
       <c r="R35" s="11"/>
@@ -3063,13 +3041,13 @@
     </row>
     <row r="36" s="4" customFormat="1" spans="2:19">
       <c r="B36" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D36" s="11" t="s">
         <v>109</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>108</v>
       </c>
       <c r="E36" s="11">
         <v>25</v>
@@ -3099,10 +3077,10 @@
       </c>
       <c r="O36" s="11"/>
       <c r="P36" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q36" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R36" s="11">
         <v>1</v>
@@ -3111,13 +3089,13 @@
     </row>
     <row r="37" s="4" customFormat="1" spans="2:19">
       <c r="B37" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E37" s="11">
         <v>12</v>
@@ -3151,7 +3129,7 @@
       </c>
       <c r="O37" s="11"/>
       <c r="P37" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q37" s="11"/>
       <c r="R37" s="11"/>
@@ -3159,13 +3137,13 @@
     </row>
     <row r="38" s="4" customFormat="1" spans="2:19">
       <c r="B38" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E38" s="11">
         <v>16</v>
@@ -3199,10 +3177,10 @@
       </c>
       <c r="O38" s="11"/>
       <c r="P38" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q38" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R38" s="11">
         <v>1</v>
@@ -3211,13 +3189,13 @@
     </row>
     <row r="39" s="4" customFormat="1" spans="2:19">
       <c r="B39" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E39" s="11">
         <v>54</v>
@@ -3247,7 +3225,7 @@
       </c>
       <c r="O39" s="11"/>
       <c r="P39" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q39" s="11"/>
       <c r="R39" s="11"/>
@@ -3255,13 +3233,13 @@
     </row>
     <row r="40" s="4" customFormat="1" spans="2:19">
       <c r="B40" s="11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E40" s="11">
         <v>67</v>
@@ -3291,10 +3269,10 @@
       </c>
       <c r="O40" s="11"/>
       <c r="P40" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q40" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="R40" s="11">
         <v>1</v>
@@ -3303,13 +3281,13 @@
     </row>
     <row r="41" s="4" customFormat="1" spans="2:19">
       <c r="B41" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E41" s="11">
         <v>120</v>
@@ -3339,7 +3317,7 @@
       </c>
       <c r="O41" s="11"/>
       <c r="P41" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q41" s="11"/>
       <c r="R41" s="11"/>
@@ -3347,13 +3325,13 @@
     </row>
     <row r="42" s="4" customFormat="1" spans="2:19">
       <c r="B42" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E42" s="11">
         <v>135</v>
@@ -3383,10 +3361,10 @@
       </c>
       <c r="O42" s="11"/>
       <c r="P42" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q42" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="R42" s="11">
         <v>1</v>
@@ -3415,13 +3393,13 @@
     </row>
     <row r="44" s="5" customFormat="1" spans="2:19">
       <c r="B44" s="12" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E44" s="12">
         <v>400</v>
@@ -3449,7 +3427,7 @@
       <c r="N44" s="12"/>
       <c r="O44" s="12"/>
       <c r="P44" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q44" s="12"/>
       <c r="R44" s="12"/>
@@ -3477,13 +3455,13 @@
     </row>
     <row r="46" spans="2:19">
       <c r="B46" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E46" s="7">
         <v>400</v>
@@ -3517,7 +3495,7 @@
       </c>
       <c r="O46" s="7"/>
       <c r="P46" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q46" s="7"/>
       <c r="R46" s="7"/>
@@ -3527,13 +3505,13 @@
     </row>
     <row r="47" spans="2:19">
       <c r="B47" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E47" s="7">
         <v>600</v>
@@ -3567,10 +3545,10 @@
       </c>
       <c r="O47" s="7"/>
       <c r="P47" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q47" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="R47" s="7">
         <v>1</v>

--- a/DataTables/Datas/#ArmyData-小队表.xlsx
+++ b/DataTables/Datas/#ArmyData-小队表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="135">
   <si>
     <t>##var</t>
   </si>
@@ -86,6 +86,9 @@
     <t>upkeep#default=1</t>
   </si>
   <si>
+    <t>radius#default=0.08</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -401,7 +404,7 @@
     <t>阴魂</t>
   </si>
   <si>
-    <t>Gore</t>
+    <t>Ogre</t>
   </si>
   <si>
     <t>食人魔</t>
@@ -1442,7 +1445,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S47"/>
+  <dimension ref="A1:T47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="6" customWidth="1"/>
@@ -1457,7 +1460,7 @@
     <col min="19" max="16384" width="8.66666666666667" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:20">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1515,69 +1518,75 @@
       <c r="S1" s="7" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:19">
+      <c r="T1" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20">
       <c r="A2" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="N2" s="7" t="s">
-        <v>23</v>
-      </c>
       <c r="O2" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="R2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="S2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="T2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="P2" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q2" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="R2" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="S2" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19">
+    </row>
+    <row r="3" spans="1:20">
       <c r="A3" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -1597,73 +1606,75 @@
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
       <c r="S3" s="7"/>
-    </row>
-    <row r="4" spans="1:19">
+      <c r="T3" s="7"/>
+    </row>
+    <row r="4" spans="1:20">
       <c r="A4" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="R4" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="S4" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:19">
+        <v>47</v>
+      </c>
+      <c r="T4" s="7"/>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:20">
       <c r="B5" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E5" s="8">
         <v>26</v>
@@ -1693,21 +1704,24 @@
       </c>
       <c r="O5" s="8"/>
       <c r="P5" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q5" s="8"/>
       <c r="R5" s="8"/>
       <c r="S5" s="8"/>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:19">
+      <c r="T5" s="8">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:20">
       <c r="B6" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E6" s="8">
         <v>36</v>
@@ -1737,25 +1751,28 @@
       </c>
       <c r="O6" s="8"/>
       <c r="P6" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="R6" s="8">
         <v>1</v>
       </c>
       <c r="S6" s="8"/>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:19">
+      <c r="T6" s="8">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:20">
       <c r="B7" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E7" s="8">
         <v>40</v>
@@ -1785,25 +1802,28 @@
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q7" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="R7" s="8">
         <v>2</v>
       </c>
       <c r="S7" s="8"/>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:19">
+      <c r="T7" s="8">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:20">
       <c r="B8" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E8" s="8">
         <v>16</v>
@@ -1837,21 +1857,24 @@
       </c>
       <c r="O8" s="8"/>
       <c r="P8" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
       <c r="S8" s="8"/>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:19">
+      <c r="T8" s="8">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:20">
       <c r="B9" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E9" s="8">
         <v>22</v>
@@ -1885,25 +1908,28 @@
       </c>
       <c r="O9" s="8"/>
       <c r="P9" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q9" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="R9" s="8">
         <v>1</v>
       </c>
       <c r="S9" s="8"/>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:19">
+      <c r="T9" s="8">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:20">
       <c r="B10" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E10" s="8">
         <v>58</v>
@@ -1933,21 +1959,22 @@
       </c>
       <c r="O10" s="8"/>
       <c r="P10" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q10" s="8"/>
       <c r="R10" s="8"/>
       <c r="S10" s="8"/>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:19">
+      <c r="T10" s="8"/>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:20">
       <c r="B11" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E11" s="8">
         <v>72</v>
@@ -1977,25 +2004,26 @@
       </c>
       <c r="O11" s="8"/>
       <c r="P11" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R11" s="8">
         <v>1</v>
       </c>
       <c r="S11" s="8"/>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:19">
+      <c r="T11" s="8"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:20">
       <c r="B12" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E12" s="8">
         <v>65</v>
@@ -2025,21 +2053,22 @@
       </c>
       <c r="O12" s="8"/>
       <c r="P12" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q12" s="8"/>
       <c r="R12" s="8"/>
       <c r="S12" s="8"/>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:19">
+      <c r="T12" s="8"/>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:20">
       <c r="B13" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E13" s="8">
         <v>75</v>
@@ -2071,25 +2100,26 @@
       </c>
       <c r="O13" s="8"/>
       <c r="P13" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q13" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="R13" s="8">
         <v>1</v>
       </c>
       <c r="S13" s="8"/>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:19">
+      <c r="T13" s="8"/>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:20">
       <c r="B14" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E14" s="8">
         <v>1000</v>
@@ -2117,13 +2147,16 @@
       <c r="N14" s="8"/>
       <c r="O14" s="8"/>
       <c r="P14" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q14" s="8"/>
       <c r="R14" s="8"/>
       <c r="S14" s="8"/>
-    </row>
-    <row r="15" spans="1:19">
+      <c r="T14" s="8">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -2142,16 +2175,17 @@
       <c r="Q15" s="7"/>
       <c r="R15" s="7"/>
       <c r="S15" s="7"/>
-    </row>
-    <row r="16" s="2" customFormat="1" spans="1:19">
+      <c r="T15" s="7"/>
+    </row>
+    <row r="16" s="2" customFormat="1" spans="1:20">
       <c r="B16" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E16" s="9">
         <v>18</v>
@@ -2181,21 +2215,24 @@
       </c>
       <c r="O16" s="9"/>
       <c r="P16" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q16" s="9"/>
       <c r="R16" s="9"/>
       <c r="S16" s="9"/>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="2:19">
+      <c r="T16" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" spans="2:20">
       <c r="B17" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>73</v>
       </c>
       <c r="E17" s="9">
         <v>25</v>
@@ -2225,25 +2262,28 @@
       </c>
       <c r="O17" s="9"/>
       <c r="P17" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q17" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="R17" s="9">
         <v>1</v>
       </c>
       <c r="S17" s="9"/>
-    </row>
-    <row r="18" s="2" customFormat="1" spans="2:19">
+      <c r="T17" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" spans="2:20">
       <c r="B18" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E18" s="9">
         <v>15</v>
@@ -2277,21 +2317,24 @@
       </c>
       <c r="O18" s="9"/>
       <c r="P18" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q18" s="9"/>
       <c r="R18" s="9"/>
       <c r="S18" s="9"/>
-    </row>
-    <row r="19" s="2" customFormat="1" spans="2:19">
+      <c r="T18" s="9">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" spans="2:20">
       <c r="B19" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E19" s="9">
         <v>18</v>
@@ -2325,25 +2368,28 @@
       </c>
       <c r="O19" s="9"/>
       <c r="P19" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q19" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="R19" s="9">
         <v>1</v>
       </c>
       <c r="S19" s="9"/>
-    </row>
-    <row r="20" s="2" customFormat="1" spans="2:19">
+      <c r="T19" s="9">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" spans="2:20">
       <c r="B20" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E20" s="9">
         <v>40</v>
@@ -2373,21 +2419,22 @@
       </c>
       <c r="O20" s="9"/>
       <c r="P20" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q20" s="9"/>
       <c r="R20" s="9"/>
       <c r="S20" s="9"/>
-    </row>
-    <row r="21" s="2" customFormat="1" spans="2:19">
+      <c r="T20" s="9"/>
+    </row>
+    <row r="21" s="2" customFormat="1" spans="2:20">
       <c r="B21" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E21" s="9">
         <v>48</v>
@@ -2417,25 +2464,26 @@
       </c>
       <c r="O21" s="9"/>
       <c r="P21" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q21" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="R21" s="9">
         <v>1</v>
       </c>
       <c r="S21" s="9"/>
-    </row>
-    <row r="22" s="2" customFormat="1" spans="2:19">
+      <c r="T21" s="9"/>
+    </row>
+    <row r="22" s="2" customFormat="1" spans="2:20">
       <c r="B22" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E22" s="9">
         <v>75</v>
@@ -2465,25 +2513,26 @@
       </c>
       <c r="O22" s="9"/>
       <c r="P22" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q22" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="R22" s="9">
         <v>2</v>
       </c>
       <c r="S22" s="9"/>
-    </row>
-    <row r="23" s="2" customFormat="1" spans="2:19">
+      <c r="T22" s="9"/>
+    </row>
+    <row r="23" s="2" customFormat="1" spans="2:20">
       <c r="B23" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E23" s="9">
         <v>120</v>
@@ -2513,13 +2562,14 @@
       </c>
       <c r="O23" s="9"/>
       <c r="P23" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q23" s="9"/>
       <c r="R23" s="9"/>
       <c r="S23" s="9"/>
-    </row>
-    <row r="24" spans="2:19">
+      <c r="T23" s="9"/>
+    </row>
+    <row r="24" spans="2:20">
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
@@ -2538,16 +2588,17 @@
       <c r="Q24" s="7"/>
       <c r="R24" s="7"/>
       <c r="S24" s="7"/>
-    </row>
-    <row r="25" s="3" customFormat="1" spans="2:19">
+      <c r="T24" s="7"/>
+    </row>
+    <row r="25" s="3" customFormat="1" spans="2:20">
       <c r="B25" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E25" s="10">
         <v>22</v>
@@ -2577,21 +2628,24 @@
       </c>
       <c r="O25" s="10"/>
       <c r="P25" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="10"/>
-    </row>
-    <row r="26" s="3" customFormat="1" spans="2:19">
+      <c r="T25" s="10">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="26" s="3" customFormat="1" spans="2:20">
       <c r="B26" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D26" s="10" t="s">
         <v>91</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>90</v>
       </c>
       <c r="E26" s="10">
         <v>28</v>
@@ -2621,25 +2675,28 @@
       </c>
       <c r="O26" s="10"/>
       <c r="P26" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q26" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="R26" s="10">
         <v>1</v>
       </c>
       <c r="S26" s="10"/>
-    </row>
-    <row r="27" s="3" customFormat="1" spans="2:19">
+      <c r="T26" s="10">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="27" s="3" customFormat="1" spans="2:20">
       <c r="B27" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E27" s="10">
         <v>14</v>
@@ -2673,21 +2730,24 @@
       </c>
       <c r="O27" s="10"/>
       <c r="P27" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="10"/>
-    </row>
-    <row r="28" s="3" customFormat="1" spans="2:19">
+      <c r="T27" s="10">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="28" s="3" customFormat="1" spans="2:20">
       <c r="B28" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E28" s="10">
         <v>27</v>
@@ -2721,25 +2781,28 @@
       </c>
       <c r="O28" s="10"/>
       <c r="P28" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q28" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="R28" s="10">
         <v>1</v>
       </c>
       <c r="S28" s="10"/>
-    </row>
-    <row r="29" s="3" customFormat="1" spans="2:19">
+      <c r="T28" s="10">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="29" s="3" customFormat="1" spans="2:20">
       <c r="B29" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E29" s="10">
         <v>200</v>
@@ -2773,25 +2836,28 @@
       </c>
       <c r="O29" s="10"/>
       <c r="P29" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q29" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="R29" s="10">
         <v>2</v>
       </c>
       <c r="S29" s="10"/>
-    </row>
-    <row r="30" s="3" customFormat="1" spans="2:19">
+      <c r="T29" s="10">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="30" s="3" customFormat="1" spans="2:20">
       <c r="B30" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E30" s="10">
         <v>54</v>
@@ -2821,21 +2887,22 @@
       </c>
       <c r="O30" s="10"/>
       <c r="P30" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q30" s="10"/>
       <c r="R30" s="10"/>
       <c r="S30" s="10"/>
-    </row>
-    <row r="31" s="3" customFormat="1" spans="2:19">
+      <c r="T30" s="10"/>
+    </row>
+    <row r="31" s="3" customFormat="1" spans="2:20">
       <c r="B31" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E31" s="10">
         <v>67</v>
@@ -2865,25 +2932,26 @@
       </c>
       <c r="O31" s="10"/>
       <c r="P31" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q31" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="R31" s="10">
         <v>1</v>
       </c>
       <c r="S31" s="10"/>
-    </row>
-    <row r="32" s="3" customFormat="1" spans="2:19">
+      <c r="T31" s="10"/>
+    </row>
+    <row r="32" s="3" customFormat="1" spans="2:20">
       <c r="B32" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E32" s="10">
         <v>55</v>
@@ -2917,21 +2985,22 @@
       </c>
       <c r="O32" s="10"/>
       <c r="P32" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q32" s="10"/>
       <c r="R32" s="10"/>
       <c r="S32" s="10"/>
-    </row>
-    <row r="33" s="3" customFormat="1" spans="2:19">
+      <c r="T32" s="10"/>
+    </row>
+    <row r="33" s="3" customFormat="1" spans="2:20">
       <c r="B33" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E33" s="10">
         <v>65</v>
@@ -2965,17 +3034,18 @@
       </c>
       <c r="O33" s="10"/>
       <c r="P33" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q33" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R33" s="10">
         <v>1</v>
       </c>
       <c r="S33" s="10"/>
-    </row>
-    <row r="34" spans="2:19">
+      <c r="T33" s="10"/>
+    </row>
+    <row r="34" spans="2:20">
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
@@ -2994,16 +3064,17 @@
       <c r="Q34" s="7"/>
       <c r="R34" s="7"/>
       <c r="S34" s="7"/>
-    </row>
-    <row r="35" s="4" customFormat="1" spans="2:19">
+      <c r="T34" s="7"/>
+    </row>
+    <row r="35" s="4" customFormat="1" spans="2:20">
       <c r="B35" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E35" s="11">
         <v>18</v>
@@ -3033,21 +3104,24 @@
       </c>
       <c r="O35" s="11"/>
       <c r="P35" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q35" s="11"/>
       <c r="R35" s="11"/>
       <c r="S35" s="11"/>
-    </row>
-    <row r="36" s="4" customFormat="1" spans="2:19">
+      <c r="T35" s="11">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="36" s="4" customFormat="1" spans="2:20">
       <c r="B36" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="D36" s="11" t="s">
         <v>110</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>109</v>
       </c>
       <c r="E36" s="11">
         <v>25</v>
@@ -3077,25 +3151,28 @@
       </c>
       <c r="O36" s="11"/>
       <c r="P36" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q36" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="R36" s="11">
         <v>1</v>
       </c>
       <c r="S36" s="11"/>
-    </row>
-    <row r="37" s="4" customFormat="1" spans="2:19">
+      <c r="T36" s="11">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="37" s="4" customFormat="1" spans="2:20">
       <c r="B37" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E37" s="11">
         <v>12</v>
@@ -3129,21 +3206,24 @@
       </c>
       <c r="O37" s="11"/>
       <c r="P37" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q37" s="11"/>
       <c r="R37" s="11"/>
       <c r="S37" s="11"/>
-    </row>
-    <row r="38" s="4" customFormat="1" spans="2:19">
+      <c r="T37" s="11">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="38" s="4" customFormat="1" spans="2:20">
       <c r="B38" s="11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E38" s="11">
         <v>16</v>
@@ -3177,25 +3257,28 @@
       </c>
       <c r="O38" s="11"/>
       <c r="P38" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q38" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="R38" s="11">
         <v>1</v>
       </c>
       <c r="S38" s="11"/>
-    </row>
-    <row r="39" s="4" customFormat="1" spans="2:19">
+      <c r="T38" s="11">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="39" s="4" customFormat="1" spans="2:20">
       <c r="B39" s="11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E39" s="11">
         <v>54</v>
@@ -3225,21 +3308,22 @@
       </c>
       <c r="O39" s="11"/>
       <c r="P39" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q39" s="11"/>
       <c r="R39" s="11"/>
       <c r="S39" s="11"/>
-    </row>
-    <row r="40" s="4" customFormat="1" spans="2:19">
+      <c r="T39" s="11"/>
+    </row>
+    <row r="40" s="4" customFormat="1" spans="2:20">
       <c r="B40" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E40" s="11">
         <v>67</v>
@@ -3269,25 +3353,26 @@
       </c>
       <c r="O40" s="11"/>
       <c r="P40" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q40" s="11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="R40" s="11">
         <v>1</v>
       </c>
       <c r="S40" s="11"/>
-    </row>
-    <row r="41" s="4" customFormat="1" spans="2:19">
+      <c r="T40" s="11"/>
+    </row>
+    <row r="41" s="4" customFormat="1" spans="2:20">
       <c r="B41" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E41" s="11">
         <v>120</v>
@@ -3317,21 +3402,22 @@
       </c>
       <c r="O41" s="11"/>
       <c r="P41" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q41" s="11"/>
       <c r="R41" s="11"/>
       <c r="S41" s="11"/>
-    </row>
-    <row r="42" s="4" customFormat="1" spans="2:19">
+      <c r="T41" s="11"/>
+    </row>
+    <row r="42" s="4" customFormat="1" spans="2:20">
       <c r="B42" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E42" s="11">
         <v>135</v>
@@ -3361,17 +3447,18 @@
       </c>
       <c r="O42" s="11"/>
       <c r="P42" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q42" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="R42" s="11">
         <v>1</v>
       </c>
       <c r="S42" s="11"/>
-    </row>
-    <row r="43" spans="2:19">
+      <c r="T42" s="11"/>
+    </row>
+    <row r="43" spans="2:20">
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
@@ -3390,16 +3477,17 @@
       <c r="Q43" s="7"/>
       <c r="R43" s="7"/>
       <c r="S43" s="7"/>
-    </row>
-    <row r="44" s="5" customFormat="1" spans="2:19">
+      <c r="T43" s="7"/>
+    </row>
+    <row r="44" s="5" customFormat="1" spans="2:20">
       <c r="B44" s="12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E44" s="12">
         <v>400</v>
@@ -3427,13 +3515,16 @@
       <c r="N44" s="12"/>
       <c r="O44" s="12"/>
       <c r="P44" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q44" s="12"/>
       <c r="R44" s="12"/>
       <c r="S44" s="12"/>
-    </row>
-    <row r="45" spans="2:19">
+      <c r="T44" s="12">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20">
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
@@ -3452,16 +3543,17 @@
       <c r="Q45" s="7"/>
       <c r="R45" s="7"/>
       <c r="S45" s="7"/>
-    </row>
-    <row r="46" spans="2:19">
+      <c r="T45" s="7"/>
+    </row>
+    <row r="46" spans="2:20">
       <c r="B46" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E46" s="7">
         <v>400</v>
@@ -3495,23 +3587,26 @@
       </c>
       <c r="O46" s="7"/>
       <c r="P46" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q46" s="7"/>
       <c r="R46" s="7"/>
       <c r="S46" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="47" spans="2:19">
+      <c r="T46" s="7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20">
       <c r="B47" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E47" s="7">
         <v>600</v>
@@ -3545,16 +3640,19 @@
       </c>
       <c r="O47" s="7"/>
       <c r="P47" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q47" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="R47" s="7">
         <v>1</v>
       </c>
       <c r="S47" s="7">
         <v>2</v>
+      </c>
+      <c r="T47" s="7">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
